--- a/client/public/Sorce/balanceML.xlsx
+++ b/client/public/Sorce/balanceML.xlsx
@@ -19,7 +19,7 @@
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 01.02.2025 11:35:12</t>
+    <t>Период: на 14.10.2025 15:55:19</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>

--- a/client/public/Sorce/balanceML.xlsx
+++ b/client/public/Sorce/balanceML.xlsx
@@ -19,7 +19,7 @@
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 14.10.2025 15:55:19</t>
+    <t>Период: на 02.12.2025 15:35:15</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>

--- a/client/public/Sorce/balanceML.xlsx
+++ b/client/public/Sorce/balanceML.xlsx
@@ -19,7 +19,7 @@
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 02.12.2025 15:35:15</t>
+    <t>Период: на 23.12.2025 16:15:14</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>

--- a/client/public/Sorce/balanceML.xlsx
+++ b/client/public/Sorce/balanceML.xlsx
@@ -19,7 +19,7 @@
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 23.12.2025 16:15:14</t>
+    <t>Период: на 16.01.2026 15:05:14</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>

--- a/client/public/Sorce/balanceML.xlsx
+++ b/client/public/Sorce/balanceML.xlsx
@@ -19,7 +19,7 @@
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 16.01.2026 15:05:14</t>
+    <t>Период: на 30.01.2026 8:15:14</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>

--- a/client/public/Sorce/balanceML.xlsx
+++ b/client/public/Sorce/balanceML.xlsx
@@ -19,7 +19,7 @@
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 30.01.2026 8:15:14</t>
+    <t>Период: на 11.02.2026 19:55:13</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>

--- a/client/public/Sorce/balanceML.xlsx
+++ b/client/public/Sorce/balanceML.xlsx
@@ -19,7 +19,7 @@
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 11.02.2026 19:55:13</t>
+    <t>Период: на 16.02.2026 7:55:14</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>

--- a/client/public/Sorce/balanceML.xlsx
+++ b/client/public/Sorce/balanceML.xlsx
@@ -19,7 +19,7 @@
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 16.02.2026 7:55:14</t>
+    <t>Период: на 23.02.2026 11:15:13</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>

--- a/client/public/Sorce/balanceML.xlsx
+++ b/client/public/Sorce/balanceML.xlsx
@@ -19,7 +19,7 @@
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 23.02.2026 11:15:13</t>
+    <t>Период: на 19.03.2026 20:05:31</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>

--- a/client/public/Sorce/balanceML.xlsx
+++ b/client/public/Sorce/balanceML.xlsx
@@ -19,7 +19,7 @@
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 19.03.2026 20:05:31</t>
+    <t>Период: на 05.04.2026 19:35:16</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
